--- a/cfg/excel/DamageCfg.xlsx
+++ b/cfg/excel/DamageCfg.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -42,13 +42,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>characterDamage</t>
+    <t>level</t>
   </si>
   <si>
-    <t>upgradeMaterial</t>
+    <t>roleId</t>
   </si>
   <si>
-    <t>upgradeUse</t>
+    <t>damageType</t>
+  </si>
+  <si>
+    <t>damage</t>
   </si>
   <si>
     <t>##type</t>
@@ -57,7 +60,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>(list#sep=,),int</t>
+    <t>DamageType</t>
   </si>
   <si>
     <t>##</t>
@@ -66,52 +69,34 @@
     <t>伤害id</t>
   </si>
   <si>
-    <t>角色伤害</t>
+    <t>等级</t>
   </si>
   <si>
-    <t>武器伤害</t>
+    <t>角色id</t>
   </si>
   <si>
-    <t>技能倍率</t>
+    <t>伤害类型</t>
   </si>
   <si>
-    <t>1,0</t>
+    <t>伤害</t>
   </si>
   <si>
-    <t>1,2001005</t>
+    <t>女警主动技能</t>
   </si>
   <si>
-    <t>1,2002005</t>
+    <t>女警被动技能</t>
   </si>
   <si>
-    <t>1,2003005</t>
+    <t>白袍主动技能</t>
   </si>
   <si>
-    <t>1,2004005</t>
+    <t>白袍被动技能</t>
   </si>
   <si>
-    <t>1,2005005</t>
+    <t>山主动技能</t>
   </si>
   <si>
-    <t>1,2006005</t>
-  </si>
-  <si>
-    <t>1,3001005</t>
-  </si>
-  <si>
-    <t>1,3002005</t>
-  </si>
-  <si>
-    <t>1,3003005</t>
-  </si>
-  <si>
-    <t>1,3004005</t>
-  </si>
-  <si>
-    <t>1,3005005</t>
-  </si>
-  <si>
-    <t>1,3006005</t>
+    <t>山被动技能</t>
   </si>
 </sst>
 </file>
@@ -541,16 +526,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -801,7 +786,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -826,32 +811,23 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" quotePrefix="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1164,17 +1140,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
     <col min="3" max="3" width="25.875" customWidth="1"/>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="33.125" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="4" max="7" width="30.875" customWidth="1"/>
+    <col min="8" max="8" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1184,385 +1159,368 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:8">
-      <c r="A2" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" s="3" customFormat="1" ht="20.25" spans="1:8">
-      <c r="A3" s="12" t="s">
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="20.25" spans="1:9">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" s="4" customFormat="1" ht="20.25" spans="1:8">
+      <c r="F3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" s="4" customFormat="1" ht="20.25" spans="1:9">
       <c r="B4" s="4">
         <v>1001</v>
       </c>
       <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B5" s="4">
         <v>1001</v>
       </c>
-      <c r="D4" s="4">
-        <v>1001001</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B5" s="4">
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B6" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B7" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B8" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B9" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="4">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B10" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C10" s="4">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B11" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C11" s="4">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B12" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C12" s="4">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B13" s="4">
+        <v>1001</v>
+      </c>
+      <c r="C13" s="4">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B14" s="4">
         <v>1002</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B15" s="4">
         <v>1002</v>
       </c>
-      <c r="D5" s="4">
-        <v>1002001</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B6" s="4">
+      <c r="C15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" ht="20.25" spans="1:9">
+      <c r="B16" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="4" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B17" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B18" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C18" s="4">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B19" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C19" s="4">
+        <v>6</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B20" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C20" s="4">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B21" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C21" s="4">
+        <v>8</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B22" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C22" s="4">
+        <v>9</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="5" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B23" s="4">
+        <v>1002</v>
+      </c>
+      <c r="C23" s="4">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="5" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B24" s="4">
         <v>1003</v>
       </c>
-      <c r="C6" s="4">
-        <v>1003</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1003001</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B7" s="4">
-        <v>1004</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1004</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1004001</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B8" s="4">
-        <v>1005</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1005</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1005001</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B9" s="4">
-        <v>1006</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1006</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1006001</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B10" s="4">
-        <v>2001</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2001</v>
-      </c>
-      <c r="D10" s="14">
-        <v>2001001</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B11" s="4">
-        <v>2002</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2002</v>
-      </c>
-      <c r="D11" s="14">
-        <v>2002001</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B12" s="4">
-        <v>2003</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2003</v>
-      </c>
-      <c r="D12" s="14">
-        <v>2003001</v>
-      </c>
-      <c r="E12" s="16" t="s">
+      <c r="C24" s="4">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B13" s="4">
-        <v>2004</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2004</v>
-      </c>
-      <c r="D13" s="14">
-        <v>2004001</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B14" s="4">
-        <v>2005</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2005</v>
-      </c>
-      <c r="D14" s="14">
-        <v>2005001</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B15" s="4">
-        <v>2006</v>
-      </c>
-      <c r="C15" s="4">
-        <v>2006</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2006001</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" s="4" customFormat="1" ht="20.25" spans="1:8">
-      <c r="B16" s="4">
-        <v>3001</v>
-      </c>
-      <c r="C16" s="4">
-        <v>3001</v>
-      </c>
-      <c r="D16" s="4">
-        <v>3001001</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="4" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B17" s="4">
-        <v>3002</v>
-      </c>
-      <c r="C17" s="4">
-        <v>3002</v>
-      </c>
-      <c r="D17" s="4">
-        <v>3002001</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" s="4" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B18" s="4">
-        <v>3003</v>
-      </c>
-      <c r="C18" s="4">
-        <v>3003</v>
-      </c>
-      <c r="D18" s="4">
-        <v>3003001</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B19" s="4">
-        <v>3004</v>
-      </c>
-      <c r="C19" s="4">
-        <v>3004</v>
-      </c>
-      <c r="D19" s="4">
-        <v>3004001</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" s="4" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B20" s="4">
-        <v>3005</v>
-      </c>
-      <c r="C20" s="4">
-        <v>3005</v>
-      </c>
-      <c r="D20" s="4">
-        <v>3005001</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" s="5" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B21" s="4">
-        <v>3006</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3006</v>
-      </c>
-      <c r="D21" s="4">
-        <v>3006001</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" s="5" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B22" s="14">
-        <v>4001</v>
-      </c>
-      <c r="C22" s="4">
-        <v>1001</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1001001</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-    </row>
-    <row r="23" s="5" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B23" s="14">
-        <v>4002</v>
-      </c>
-      <c r="C23" s="4">
-        <v>1002</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1002001</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-    </row>
-    <row r="24" s="5" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B24" s="14">
-        <v>4003</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1003</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1003001</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>13</v>
+      <c r="E24" s="4">
+        <v>1000</v>
       </c>
       <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -1579,22 +1537,23 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
-    </row>
-    <row r="25" s="5" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B25" s="14">
-        <v>4004</v>
+      <c r="X24" s="4"/>
+    </row>
+    <row r="25" s="5" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B25" s="4">
+        <v>1003</v>
       </c>
       <c r="C25" s="4">
-        <v>1004</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1004001</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4">
+        <v>1000</v>
       </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1611,150 +1570,155 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
-    </row>
-    <row r="26" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B26" s="14">
-        <v>4005</v>
+      <c r="X25" s="4"/>
+    </row>
+    <row r="26" s="5" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B26" s="4">
+        <v>1003</v>
       </c>
       <c r="C26" s="4">
-        <v>1005</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1005001</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-    </row>
-    <row r="27" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B27" s="14">
-        <v>4006</v>
+        <v>3</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+    </row>
+    <row r="27" s="5" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B27" s="4">
+        <v>1003</v>
       </c>
       <c r="C27" s="4">
-        <v>1006</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1006001</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-    </row>
-    <row r="28" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B28" s="14">
-        <v>5001</v>
+        <v>4</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+    </row>
+    <row r="28" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B28" s="4">
+        <v>1003</v>
       </c>
       <c r="C28" s="4">
-        <v>1001</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1001001</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4">
+        <v>1000</v>
       </c>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-    </row>
-    <row r="29" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B29" s="14">
-        <v>5002</v>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+      <c r="X28" s="11"/>
+    </row>
+    <row r="29" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B29" s="4">
+        <v>1003</v>
       </c>
       <c r="C29" s="4">
-        <v>1002</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1002001</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4">
+        <v>1000</v>
       </c>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-    </row>
-    <row r="30" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B30" s="14">
-        <v>5003</v>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+    </row>
+    <row r="30" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B30" s="4">
+        <v>1003</v>
       </c>
       <c r="C30" s="4">
-        <v>1003</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1003001</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4">
+        <v>1000</v>
       </c>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="G30" s="4">
+        <v>0</v>
+      </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1769,24 +1733,25 @@
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
-    </row>
-    <row r="31" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B31" s="14">
-        <v>5004</v>
+      <c r="V30" s="4"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+    </row>
+    <row r="31" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B31" s="4">
+        <v>1003</v>
       </c>
       <c r="C31" s="4">
-        <v>1004</v>
-      </c>
-      <c r="D31" s="4">
-        <v>1004001</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4">
+        <v>1000</v>
       </c>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="G31" s="4">
+        <v>0</v>
+      </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -1801,24 +1766,25 @@
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="15"/>
-    </row>
-    <row r="32" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B32" s="14">
-        <v>5005</v>
+      <c r="V31" s="4"/>
+      <c r="W31" s="11"/>
+      <c r="X31" s="11"/>
+    </row>
+    <row r="32" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B32" s="4">
+        <v>1003</v>
       </c>
       <c r="C32" s="4">
-        <v>1005</v>
-      </c>
-      <c r="D32" s="4">
-        <v>1005001</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4">
+        <v>1000</v>
       </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1833,24 +1799,25 @@
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
-      <c r="V32" s="15"/>
-      <c r="W32" s="15"/>
-    </row>
-    <row r="33" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B33" s="14">
-        <v>5006</v>
+      <c r="V32" s="4"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+    </row>
+    <row r="33" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B33" s="4">
+        <v>1003</v>
       </c>
       <c r="C33" s="4">
-        <v>1006</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1006001</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4">
+        <v>1000</v>
       </c>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="G33" s="4">
+        <v>0</v>
+      </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -1865,24 +1832,27 @@
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
-    </row>
-    <row r="34" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B34" s="14">
-        <v>6001</v>
+      <c r="V33" s="4"/>
+      <c r="W33" s="11"/>
+      <c r="X33" s="11"/>
+    </row>
+    <row r="34" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B34" s="4">
+        <v>2001</v>
       </c>
       <c r="C34" s="4">
-        <v>1001</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1001001</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="4">
+        <v>2000</v>
       </c>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="G34" s="4">
+        <v>75</v>
+      </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -1897,24 +1867,25 @@
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
-      <c r="V34" s="15"/>
-      <c r="W34" s="15"/>
-    </row>
-    <row r="35" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B35" s="14">
-        <v>6002</v>
+      <c r="V34" s="4"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="11"/>
+    </row>
+    <row r="35" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B35" s="4">
+        <v>2001</v>
       </c>
       <c r="C35" s="4">
-        <v>1002</v>
-      </c>
-      <c r="D35" s="4">
-        <v>1002001</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4">
+        <v>2000</v>
       </c>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="G35" s="4">
+        <v>80</v>
+      </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -1929,24 +1900,25 @@
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-    </row>
-    <row r="36" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B36" s="14">
-        <v>6003</v>
+      <c r="V35" s="4"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+    </row>
+    <row r="36" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B36" s="4">
+        <v>2001</v>
       </c>
       <c r="C36" s="4">
-        <v>1003</v>
-      </c>
-      <c r="D36" s="4">
-        <v>1003001</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>13</v>
+        <v>3</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4">
+        <v>2000</v>
       </c>
       <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="G36" s="4">
+        <v>85</v>
+      </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -1961,24 +1933,25 @@
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-    </row>
-    <row r="37" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B37" s="14">
-        <v>6004</v>
+      <c r="V36" s="4"/>
+      <c r="W36" s="11"/>
+      <c r="X36" s="11"/>
+    </row>
+    <row r="37" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B37" s="4">
+        <v>2001</v>
       </c>
       <c r="C37" s="4">
-        <v>1004</v>
-      </c>
-      <c r="D37" s="4">
-        <v>1004001</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>13</v>
+        <v>4</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4">
+        <v>2000</v>
       </c>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="G37" s="4">
+        <v>90</v>
+      </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -1993,24 +1966,25 @@
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-    </row>
-    <row r="38" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B38" s="14">
-        <v>6005</v>
+      <c r="V37" s="4"/>
+      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
+    </row>
+    <row r="38" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B38" s="4">
+        <v>2001</v>
       </c>
       <c r="C38" s="4">
-        <v>1005</v>
-      </c>
-      <c r="D38" s="4">
-        <v>1005001</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4">
+        <v>2000</v>
       </c>
       <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
+      <c r="G38" s="4">
+        <v>95</v>
+      </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -2025,24 +1999,25 @@
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-    </row>
-    <row r="39" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B39" s="14">
-        <v>6006</v>
+      <c r="V38" s="4"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+    </row>
+    <row r="39" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B39" s="4">
+        <v>2001</v>
       </c>
       <c r="C39" s="4">
-        <v>1006</v>
-      </c>
-      <c r="D39" s="4">
-        <v>1006001</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4">
+        <v>2000</v>
       </c>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+      <c r="G39" s="4">
+        <v>105</v>
+      </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -2057,24 +2032,25 @@
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-    </row>
-    <row r="40" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B40" s="14">
-        <v>7001</v>
+      <c r="V39" s="4"/>
+      <c r="W39" s="11"/>
+      <c r="X39" s="11"/>
+    </row>
+    <row r="40" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B40" s="4">
+        <v>2001</v>
       </c>
       <c r="C40" s="4">
-        <v>1001</v>
-      </c>
-      <c r="D40" s="4">
-        <v>1001001</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4">
+        <v>2000</v>
       </c>
       <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="G40" s="4">
+        <v>115</v>
+      </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2089,24 +2065,25 @@
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-    </row>
-    <row r="41" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B41" s="14">
-        <v>7002</v>
+      <c r="V40" s="4"/>
+      <c r="W40" s="11"/>
+      <c r="X40" s="11"/>
+    </row>
+    <row r="41" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B41" s="4">
+        <v>2001</v>
       </c>
       <c r="C41" s="4">
-        <v>1002</v>
-      </c>
-      <c r="D41" s="4">
-        <v>1002001</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4">
+        <v>2000</v>
       </c>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
+      <c r="G41" s="4">
+        <v>130</v>
+      </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -2121,24 +2098,25 @@
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
-    </row>
-    <row r="42" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B42" s="14">
-        <v>7003</v>
+      <c r="V41" s="4"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+    </row>
+    <row r="42" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B42" s="4">
+        <v>2001</v>
       </c>
       <c r="C42" s="4">
-        <v>1003</v>
-      </c>
-      <c r="D42" s="4">
-        <v>1003001</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4">
+        <v>2000</v>
       </c>
       <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="4">
+        <v>145</v>
+      </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -2153,24 +2131,25 @@
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
-      <c r="V42" s="15"/>
-      <c r="W42" s="15"/>
-    </row>
-    <row r="43" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B43" s="14">
-        <v>7004</v>
+      <c r="V42" s="4"/>
+      <c r="W42" s="11"/>
+      <c r="X42" s="11"/>
+    </row>
+    <row r="43" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B43" s="4">
+        <v>2001</v>
       </c>
       <c r="C43" s="4">
-        <v>1004</v>
-      </c>
-      <c r="D43" s="4">
-        <v>1004001</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4">
+        <v>2000</v>
       </c>
       <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
+      <c r="G43" s="4">
+        <v>160</v>
+      </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2185,24 +2164,27 @@
       <c r="S43" s="4"/>
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
-      <c r="V43" s="15"/>
-      <c r="W43" s="15"/>
-    </row>
-    <row r="44" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B44" s="14">
-        <v>7005</v>
+      <c r="V43" s="4"/>
+      <c r="W43" s="11"/>
+      <c r="X43" s="11"/>
+    </row>
+    <row r="44" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B44" s="4">
+        <v>2002</v>
       </c>
       <c r="C44" s="4">
-        <v>1005</v>
-      </c>
-      <c r="D44" s="4">
-        <v>1005001</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="4">
+        <v>2000</v>
       </c>
       <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -2217,24 +2199,25 @@
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="15"/>
-    </row>
-    <row r="45" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B45" s="14">
-        <v>7006</v>
+      <c r="V44" s="4"/>
+      <c r="W44" s="11"/>
+      <c r="X44" s="11"/>
+    </row>
+    <row r="45" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B45" s="4">
+        <v>2002</v>
       </c>
       <c r="C45" s="4">
-        <v>1006</v>
-      </c>
-      <c r="D45" s="4">
-        <v>1006001</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4">
+        <v>2000</v>
       </c>
       <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
+      <c r="G45" s="4">
+        <v>0</v>
+      </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -2249,24 +2232,25 @@
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
-      <c r="V45" s="15"/>
-      <c r="W45" s="15"/>
-    </row>
-    <row r="46" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B46" s="14">
-        <v>8001</v>
+      <c r="V45" s="4"/>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+    </row>
+    <row r="46" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B46" s="4">
+        <v>2002</v>
       </c>
       <c r="C46" s="4">
-        <v>1001</v>
-      </c>
-      <c r="D46" s="4">
-        <v>1001001</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>13</v>
+        <v>3</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4">
+        <v>2000</v>
       </c>
       <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2281,24 +2265,25 @@
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
-      <c r="V46" s="15"/>
-      <c r="W46" s="15"/>
-    </row>
-    <row r="47" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B47" s="14">
-        <v>8002</v>
+      <c r="V46" s="4"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+    </row>
+    <row r="47" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B47" s="4">
+        <v>2002</v>
       </c>
       <c r="C47" s="4">
-        <v>1002</v>
-      </c>
-      <c r="D47" s="4">
-        <v>1002001</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>13</v>
+        <v>4</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4">
+        <v>2000</v>
       </c>
       <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
+      <c r="G47" s="4">
+        <v>0</v>
+      </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -2313,24 +2298,25 @@
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
-      <c r="V47" s="15"/>
-      <c r="W47" s="15"/>
-    </row>
-    <row r="48" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B48" s="14">
-        <v>8003</v>
+      <c r="V47" s="4"/>
+      <c r="W47" s="11"/>
+      <c r="X47" s="11"/>
+    </row>
+    <row r="48" s="6" customFormat="1" ht="20.25" spans="2:24">
+      <c r="B48" s="4">
+        <v>2002</v>
       </c>
       <c r="C48" s="4">
-        <v>1003</v>
-      </c>
-      <c r="D48" s="4">
-        <v>1003001</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4">
+        <v>2000</v>
       </c>
       <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="G48" s="4">
+        <v>0</v>
+      </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -2345,24 +2331,25 @@
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
-      <c r="V48" s="15"/>
-      <c r="W48" s="15"/>
-    </row>
-    <row r="49" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B49" s="14">
-        <v>8004</v>
+      <c r="V48" s="4"/>
+      <c r="W48" s="11"/>
+      <c r="X48" s="11"/>
+    </row>
+    <row r="49" s="6" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B49" s="4">
+        <v>2002</v>
       </c>
       <c r="C49" s="4">
-        <v>1004</v>
-      </c>
-      <c r="D49" s="4">
-        <v>1004001</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4">
+        <v>2000</v>
       </c>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="G49" s="4">
+        <v>0</v>
+      </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -2377,24 +2364,25 @@
       <c r="S49" s="4"/>
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
-      <c r="V49" s="15"/>
-      <c r="W49" s="15"/>
-    </row>
-    <row r="50" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B50" s="14">
-        <v>8005</v>
+      <c r="V49" s="4"/>
+      <c r="W49" s="11"/>
+      <c r="X49" s="11"/>
+    </row>
+    <row r="50" s="6" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B50" s="4">
+        <v>2002</v>
       </c>
       <c r="C50" s="4">
-        <v>1005</v>
-      </c>
-      <c r="D50" s="4">
-        <v>1005001</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4">
+        <v>2000</v>
       </c>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="G50" s="4">
+        <v>0</v>
+      </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2409,24 +2397,25 @@
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-    </row>
-    <row r="51" s="6" customFormat="1" ht="20.25" spans="2:23">
-      <c r="B51" s="14">
-        <v>8006</v>
+      <c r="V50" s="4"/>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+    </row>
+    <row r="51" s="6" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B51" s="4">
+        <v>2002</v>
       </c>
       <c r="C51" s="4">
-        <v>1006</v>
-      </c>
-      <c r="D51" s="4">
-        <v>1006001</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4">
+        <v>2000</v>
       </c>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="G51" s="4">
+        <v>0</v>
+      </c>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -2441,9 +2430,1268 @@
       <c r="S51" s="4"/>
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-    </row>
+      <c r="V51" s="4"/>
+      <c r="W51" s="11"/>
+      <c r="X51" s="11"/>
+    </row>
+    <row r="52" s="6" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B52" s="4">
+        <v>2002</v>
+      </c>
+      <c r="C52" s="4">
+        <v>9</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="11"/>
+      <c r="X52" s="11"/>
+    </row>
+    <row r="53" s="6" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B53" s="4">
+        <v>2002</v>
+      </c>
+      <c r="C53" s="4">
+        <v>10</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="11"/>
+      <c r="X53" s="11"/>
+    </row>
+    <row r="54" ht="20.25" spans="1:26">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C54" s="4">
+        <v>1</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4">
+        <v>0</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+    </row>
+    <row r="55" ht="20.25" spans="1:26">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C55" s="4">
+        <v>2</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+    </row>
+    <row r="56" ht="20.25" spans="1:26">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C56" s="4">
+        <v>3</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+    </row>
+    <row r="57" ht="20.25" spans="1:26">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C57" s="4">
+        <v>4</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+    </row>
+    <row r="58" ht="20.25" spans="1:26">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C58" s="4">
+        <v>5</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+    </row>
+    <row r="59" ht="20.25" spans="1:26">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C59" s="4">
+        <v>6</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4">
+        <v>0</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+    </row>
+    <row r="60" ht="20.25" spans="1:26">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C60" s="4">
+        <v>7</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4">
+        <v>0</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+    </row>
+    <row r="61" ht="20.25" spans="1:26">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C61" s="4">
+        <v>8</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" ht="20.25" spans="1:26">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C62" s="4">
+        <v>9</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+    </row>
+    <row r="63" ht="20.25" spans="1:26">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C63" s="4">
+        <v>10</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+    </row>
+    <row r="64" ht="20.25" spans="1:26">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C64" s="4">
+        <v>1</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4">
+        <v>30</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+    </row>
+    <row r="65" ht="20.25" spans="1:26">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C65" s="4">
+        <v>2</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4">
+        <v>35</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+    </row>
+    <row r="66" ht="20.25" spans="1:26">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C66" s="4">
+        <v>3</v>
+      </c>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4">
+        <v>40</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+    </row>
+    <row r="67" ht="20.25" spans="1:26">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C67" s="4">
+        <v>4</v>
+      </c>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4">
+        <v>45</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+    </row>
+    <row r="68" ht="20.25" spans="1:26">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C68" s="4">
+        <v>5</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4">
+        <v>50</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+    </row>
+    <row r="69" ht="20.25" spans="1:26">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C69" s="4">
+        <v>6</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4">
+        <v>60</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+    </row>
+    <row r="70" ht="20.25" spans="1:26">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C70" s="4">
+        <v>7</v>
+      </c>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4">
+        <v>70</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+    </row>
+    <row r="71" ht="20.25" spans="1:26">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C71" s="4">
+        <v>8</v>
+      </c>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4">
+        <v>80</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="4"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+    </row>
+    <row r="72" ht="20.25" spans="1:26">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C72" s="4">
+        <v>9</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4">
+        <v>95</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="4"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+    </row>
+    <row r="73" ht="20.25" spans="1:26">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4">
+        <v>3001</v>
+      </c>
+      <c r="C73" s="4">
+        <v>10</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4">
+        <v>105</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="S73" s="4"/>
+      <c r="T73" s="4"/>
+      <c r="U73" s="4"/>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+    </row>
+    <row r="74" ht="20.25" spans="1:26">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C74" s="4">
+        <v>1</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4">
+        <v>0</v>
+      </c>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+    </row>
+    <row r="75" ht="20.25" spans="1:26">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C75" s="4">
+        <v>2</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4">
+        <v>0</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+    </row>
+    <row r="76" ht="20.25" spans="1:26">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C76" s="4">
+        <v>3</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4">
+        <v>0</v>
+      </c>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+    </row>
+    <row r="77" ht="20.25" spans="1:26">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C77" s="4">
+        <v>4</v>
+      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+    </row>
+    <row r="78" ht="20.25" spans="1:26">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C78" s="4">
+        <v>5</v>
+      </c>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+    </row>
+    <row r="79" ht="20.25" spans="1:26">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C79" s="4">
+        <v>6</v>
+      </c>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+    </row>
+    <row r="80" ht="20.25" spans="1:26">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C80" s="4">
+        <v>7</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4">
+        <v>0</v>
+      </c>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
+      <c r="S80" s="4"/>
+      <c r="T80" s="4"/>
+      <c r="U80" s="4"/>
+      <c r="V80" s="4"/>
+      <c r="W80" s="4"/>
+      <c r="X80" s="4"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="4"/>
+    </row>
+    <row r="81" ht="20.25" spans="1:26">
+      <c r="A81" s="12"/>
+      <c r="B81" s="12">
+        <v>3002</v>
+      </c>
+      <c r="C81" s="12">
+        <v>8</v>
+      </c>
+      <c r="D81" s="12"/>
+      <c r="E81" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F81" s="13"/>
+      <c r="G81" s="12">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="12"/>
+      <c r="P81" s="12"/>
+      <c r="Q81" s="12"/>
+      <c r="R81" s="12"/>
+      <c r="S81" s="12"/>
+      <c r="T81" s="12"/>
+      <c r="U81" s="12"/>
+      <c r="V81" s="12"/>
+      <c r="W81" s="12"/>
+      <c r="X81" s="12"/>
+      <c r="Y81" s="12"/>
+      <c r="Z81" s="12"/>
+    </row>
+    <row r="82" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B82" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C82" s="4">
+        <v>9</v>
+      </c>
+      <c r="E82" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G82" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B83" s="4">
+        <v>3002</v>
+      </c>
+      <c r="C83" s="4">
+        <v>10</v>
+      </c>
+      <c r="E83" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G83" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B84" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C84" s="4">
+        <v>1</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B85" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C85" s="4">
+        <v>2</v>
+      </c>
+      <c r="E85" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B86" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C86" s="4">
+        <v>3</v>
+      </c>
+      <c r="E86" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B87" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C87" s="4">
+        <v>4</v>
+      </c>
+      <c r="E87" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B88" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C88" s="4">
+        <v>5</v>
+      </c>
+      <c r="E88" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G88" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B89" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C89" s="4">
+        <v>6</v>
+      </c>
+      <c r="E89" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G89" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B90" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C90" s="4">
+        <v>7</v>
+      </c>
+      <c r="E90" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G90" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B91" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C91" s="4">
+        <v>8</v>
+      </c>
+      <c r="E91" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B92" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C92" s="4">
+        <v>9</v>
+      </c>
+      <c r="E92" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G92" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" s="4" customFormat="1" ht="20.25" spans="1:26">
+      <c r="B93" s="4">
+        <v>3003</v>
+      </c>
+      <c r="C93" s="4">
+        <v>10</v>
+      </c>
+      <c r="E93" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G93" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" s="4" customFormat="1" ht="20.25"/>
+    <row r="95" s="4" customFormat="1" ht="20.25"/>
+    <row r="96" s="4" customFormat="1" ht="20.25"/>
+    <row r="97" s="4" customFormat="1" ht="20.25"/>
+    <row r="98" s="4" customFormat="1" ht="20.25"/>
+    <row r="99" s="4" customFormat="1" ht="20.25"/>
+    <row r="100" s="4" customFormat="1" ht="20.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
